--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2020_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2020_aysen.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:10</t>
+    <t xml:space="preserve">2026-09-24 01:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -681,13 +681,13 @@
         <v>10</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -704,13 +704,13 @@
         <v>10</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="10">
@@ -730,10 +730,10 @@
         <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="11">
@@ -744,19 +744,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="12">
